--- a/artfynd/A 42266-2026 artfynd.xlsx
+++ b/artfynd/A 42266-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ25"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6747016</v>
+        <v>137428924</v>
       </c>
       <c r="B2" t="n">
-        <v>80305</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>392</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>St Stensjön N-ut, Vstm</t>
+          <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499756</v>
+        <v>499852</v>
       </c>
       <c r="R2" t="n">
-        <v>6592840</v>
+        <v>6592928</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1995-01-01</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1995-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fyndets ursprung: 1995, Peter Alverblad. Källa: Länsstyrelsen i Örebro läns rödlistedatabas</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,75 +763,72 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Alverblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro läns rödlistedatabas</t>
-        </is>
-      </c>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6747016</t>
+          <t>https://artportalen.se/Sighting/137428924</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97621009</v>
+        <v>6747016</v>
       </c>
       <c r="B3" t="n">
-        <v>97733</v>
+        <v>80305</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>392</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dammsjön SV, Vstm</t>
+          <t>St Stensjön N-ut, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499664</v>
+        <v>499756</v>
       </c>
       <c r="R3" t="n">
-        <v>6592875</v>
+        <v>6592840</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,12 +852,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>1995-01-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>1995-12-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fyndets ursprung: 1995, Peter Alverblad. Källa: Länsstyrelsen i Örebro läns rödlistedatabas</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,65 +877,72 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Peter Alverblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro läns rödlistedatabas</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97621009</t>
+          <t>https://artportalen.se/Sighting/6747016</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97620984</v>
+        <v>137428938</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499779</v>
+        <v>499772</v>
       </c>
       <c r="R4" t="n">
-        <v>6592836</v>
+        <v>6592768</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -958,12 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -972,72 +980,72 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97620984</t>
+          <t>https://artportalen.se/Sighting/137428938</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97611270</v>
+        <v>97621009</v>
       </c>
       <c r="B5" t="n">
-        <v>93197</v>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nora, Vstm</t>
+          <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499739</v>
+        <v>499664</v>
       </c>
       <c r="R5" t="n">
-        <v>6592649</v>
+        <v>6592875</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,27 +1089,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97611270</t>
+          <t>https://artportalen.se/Sighting/97621009</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97610699</v>
+        <v>97620984</v>
       </c>
       <c r="B6" t="n">
-        <v>91872</v>
+        <v>96348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,38 +1117,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nora, Vstm</t>
+          <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499708</v>
+        <v>499779</v>
       </c>
       <c r="R6" t="n">
-        <v>6592826</v>
+        <v>6592836</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,49 +1191,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97610699</t>
+          <t>https://artportalen.se/Sighting/97620984</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97610716</v>
+        <v>97611270</v>
       </c>
       <c r="B7" t="n">
-        <v>91872</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1237,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499709</v>
+        <v>499739</v>
       </c>
       <c r="R7" t="n">
-        <v>6592814</v>
+        <v>6592649</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1298,13 +1305,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97610716</t>
+          <t>https://artportalen.se/Sighting/97611270</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97610787</v>
+        <v>97610699</v>
       </c>
       <c r="B8" t="n">
         <v>91872</v>
@@ -1340,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499735</v>
+        <v>499708</v>
       </c>
       <c r="R8" t="n">
-        <v>6592817</v>
+        <v>6592826</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1401,13 +1408,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97610787</t>
+          <t>https://artportalen.se/Sighting/97610699</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97610889</v>
+        <v>97610716</v>
       </c>
       <c r="B9" t="n">
         <v>91872</v>
@@ -1443,10 +1450,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499721</v>
+        <v>499709</v>
       </c>
       <c r="R9" t="n">
-        <v>6592788</v>
+        <v>6592814</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1476,19 +1483,9 @@
           <t>2021-12-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1503,24 +1500,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ylva Wallin</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ylva Wallin</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97610889</t>
+          <t>https://artportalen.se/Sighting/97610716</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97611775</v>
+        <v>97610787</v>
       </c>
       <c r="B10" t="n">
         <v>91872</v>
@@ -1556,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499783</v>
+        <v>499735</v>
       </c>
       <c r="R10" t="n">
-        <v>6592563</v>
+        <v>6592817</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1617,13 +1614,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97611775</t>
+          <t>https://artportalen.se/Sighting/97610787</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97611783</v>
+        <v>97610889</v>
       </c>
       <c r="B11" t="n">
         <v>91872</v>
@@ -1651,11 +1648,7 @@
           <t>(Schwein.) Murrill</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1663,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499771</v>
+        <v>499721</v>
       </c>
       <c r="R11" t="n">
-        <v>6592569</v>
+        <v>6592788</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1696,9 +1689,19 @@
           <t>2021-12-18</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1713,24 +1716,24 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Git Katarina Lundström</t>
+          <t>Ylva Wallin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Git Katarina Lundström</t>
+          <t>Ylva Wallin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97611783</t>
+          <t>https://artportalen.se/Sighting/97610889</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97620987</v>
+        <v>97611775</v>
       </c>
       <c r="B12" t="n">
         <v>91872</v>
@@ -1759,19 +1762,20 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dammsjön SV, Vstm</t>
+          <t>Nora, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>499783</v>
       </c>
       <c r="R12" t="n">
-        <v>6592763</v>
+        <v>6592563</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1815,27 +1819,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97620987</t>
+          <t>https://artportalen.se/Sighting/97611775</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97621006</v>
+        <v>97611783</v>
       </c>
       <c r="B13" t="n">
-        <v>80467</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,37 +1847,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dammsjön SV, Vstm</t>
+          <t>Nora, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499734</v>
+        <v>499771</v>
       </c>
       <c r="R13" t="n">
-        <v>6592769</v>
+        <v>6592569</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1917,72 +1926,65 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Git Katarina Lundström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Git Katarina Lundström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97621006</t>
+          <t>https://artportalen.se/Sighting/97611783</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97610586</v>
+        <v>97620987</v>
       </c>
       <c r="B14" t="n">
-        <v>57953</v>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nora, Vstm</t>
+          <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499717</v>
+        <v>499783</v>
       </c>
       <c r="R14" t="n">
-        <v>6592848</v>
+        <v>6592763</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2026,72 +2028,68 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97610586</t>
+          <t>https://artportalen.se/Sighting/97620987</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97611357</v>
+        <v>137428937</v>
       </c>
       <c r="B15" t="n">
-        <v>57953</v>
+        <v>92144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nora, Vstm</t>
+          <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499757</v>
+        <v>499784</v>
       </c>
       <c r="R15" t="n">
-        <v>6592561</v>
+        <v>6592769</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2115,12 +2113,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2129,82 +2127,76 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97611357</t>
+          <t>https://artportalen.se/Sighting/137428937</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97612130</v>
+        <v>137427830</v>
       </c>
       <c r="B16" t="n">
-        <v>57953</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nora, Vstm</t>
+          <t>Mörtabäcken, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499775</v>
+        <v>499729</v>
       </c>
       <c r="R16" t="n">
-        <v>6592759</v>
+        <v>6592821</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2228,12 +2220,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2248,49 +2250,49 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97612130</t>
+          <t>https://artportalen.se/Sighting/137427830</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97620996</v>
+        <v>97621006</v>
       </c>
       <c r="B17" t="n">
-        <v>57953</v>
+        <v>80467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499877</v>
+        <v>499734</v>
       </c>
       <c r="R17" t="n">
-        <v>6592559</v>
+        <v>6592769</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2338,11 +2340,6 @@
           <t>2021-12-18</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hackspår på gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2366,16 +2363,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97620996</t>
+          <t>https://artportalen.se/Sighting/97621006</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97620989</v>
+        <v>137424153</v>
       </c>
       <c r="B18" t="n">
-        <v>4775</v>
+        <v>58032</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,42 +2380,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dammsjön SV, Vstm</t>
+          <t>Mörtabäcken, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499789</v>
+        <v>499861</v>
       </c>
       <c r="R18" t="n">
-        <v>6592695</v>
+        <v>6592903</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2442,12 +2439,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2462,27 +2469,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97620989</t>
+          <t>https://artportalen.se/Sighting/137424153</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97620992</v>
+        <v>137425987</v>
       </c>
       <c r="B19" t="n">
-        <v>4775</v>
+        <v>58032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2490,42 +2497,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Dammsjön SV, Vstm</t>
+          <t>Mörtabäcken, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499834</v>
+        <v>499984</v>
       </c>
       <c r="R19" t="n">
-        <v>6592637</v>
+        <v>6592946</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2549,12 +2556,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2569,27 +2586,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97620992</t>
+          <t>https://artportalen.se/Sighting/137425987</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>97620994</v>
+        <v>137428916</v>
       </c>
       <c r="B20" t="n">
-        <v>4775</v>
+        <v>58032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2597,42 +2614,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499912</v>
+        <v>499714</v>
       </c>
       <c r="R20" t="n">
-        <v>6592539</v>
+        <v>6592864</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2656,12 +2672,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2676,27 +2692,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97620994</t>
+          <t>https://artportalen.se/Sighting/137428916</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>97621003</v>
+        <v>137428932</v>
       </c>
       <c r="B21" t="n">
-        <v>4775</v>
+        <v>58032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2704,42 +2720,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499714</v>
+        <v>499982</v>
       </c>
       <c r="R21" t="n">
-        <v>6592733</v>
+        <v>6592826</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2763,12 +2778,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2783,70 +2798,72 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97621003</t>
+          <t>https://artportalen.se/Sighting/137428932</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>97621007</v>
+        <v>97610586</v>
       </c>
       <c r="B22" t="n">
-        <v>4775</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dammsjön SV, Vstm</t>
+          <t>Nora, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499730</v>
+        <v>499717</v>
       </c>
       <c r="R22" t="n">
-        <v>6592780</v>
+        <v>6592848</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2890,65 +2907,72 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97621007</t>
+          <t>https://artportalen.se/Sighting/97610586</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>97621002</v>
+        <v>97611357</v>
       </c>
       <c r="B23" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dammsjön SV, Vstm</t>
+          <t>Nora, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499717</v>
+        <v>499757</v>
       </c>
       <c r="R23" t="n">
-        <v>6592666</v>
+        <v>6592561</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2992,70 +3016,76 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97621002</t>
+          <t>https://artportalen.se/Sighting/97611357</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>97621008</v>
+        <v>97612130</v>
       </c>
       <c r="B24" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dammsjön SV, Vstm</t>
+          <t>Nora, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499714</v>
+        <v>499775</v>
       </c>
       <c r="R24" t="n">
-        <v>6592786</v>
+        <v>6592759</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,44 +3129,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97621008</t>
+          <t>https://artportalen.se/Sighting/97612130</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>97620995</v>
+        <v>97620996</v>
       </c>
       <c r="B25" t="n">
-        <v>58327</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3145,21 +3175,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499898</v>
+        <v>499877</v>
       </c>
       <c r="R25" t="n">
-        <v>6592546</v>
+        <v>6592559</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3194,6 +3219,11 @@
           <t>2021-12-18</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hackspår på gran.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3217,7 +3247,964 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/97620996</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>97620989</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Dammsjön SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>499789</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6592695</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97620989</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>97620992</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Dammsjön SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>499834</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6592637</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97620992</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>97620994</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Dammsjön SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>499912</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6592539</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97620994</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>97621003</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Dammsjön SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>499714</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6592733</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97621003</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>97621007</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Dammsjön SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>499730</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6592780</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97621007</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>97621002</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Dammsjön SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>499717</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6592666</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97621002</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>97621008</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Dammsjön SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>499714</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6592786</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97621008</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>97620995</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Dammsjön SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>499898</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6592546</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/97620995</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137428918</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58191</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Dammsjön SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>499782</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6592897</v>
+      </c>
+      <c r="S34" t="n">
+        <v>50</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428918</t>
         </is>
       </c>
     </row>
@@ -3247,6 +4234,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42266-2026 artfynd.xlsx
+++ b/artfynd/A 42266-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137428924</v>
       </c>
       <c r="B2" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137428938</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>137428937</v>
       </c>
       <c r="B15" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137427830</v>
       </c>
       <c r="B16" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 42266-2026 artfynd.xlsx
+++ b/artfynd/A 42266-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137428924</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137428938</v>
       </c>
       <c r="B4" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>137428937</v>
       </c>
       <c r="B15" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>137427830</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 42266-2026 artfynd.xlsx
+++ b/artfynd/A 42266-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,52 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137428924</v>
+        <v>6747016</v>
       </c>
       <c r="B2" t="n">
-        <v>97671</v>
+        <v>80305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>392</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dammsjön SV, Vstm</t>
+          <t>St Stensjön N-ut, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499852</v>
+        <v>499756</v>
       </c>
       <c r="R2" t="n">
-        <v>6592928</v>
+        <v>6592840</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>1995-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>1995-12-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fyndets ursprung: 1995, Peter Alverblad. Källa: Länsstyrelsen i Örebro läns rödlistedatabas</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,72 +764,78 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Björn Gunnarsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Peter Alverblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro läns rödlistedatabas</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137428924</t>
+          <t>https://artportalen.se/Sighting/6747016</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6747016</v>
+        <v>137428938</v>
       </c>
       <c r="B3" t="n">
-        <v>80305</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>392</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>St Stensjön N-ut, Vstm</t>
+          <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499756</v>
+        <v>499772</v>
       </c>
       <c r="R3" t="n">
-        <v>6592840</v>
+        <v>6592768</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,17 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1995-01-01</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1995-12-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fyndets ursprung: 1995, Peter Alverblad. Källa: Länsstyrelsen i Örebro läns rödlistedatabas</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,78 +873,72 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Björn Gunnarsson</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Alverblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro läns rödlistedatabas</t>
-        </is>
-      </c>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6747016</t>
+          <t>https://artportalen.se/Sighting/137428938</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137428938</v>
+        <v>97621009</v>
       </c>
       <c r="B4" t="n">
-        <v>92185</v>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499772</v>
+        <v>499664</v>
       </c>
       <c r="R4" t="n">
-        <v>6592768</v>
+        <v>6592875</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,12 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2021-12-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2021-12-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,34 +976,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137428938</t>
+          <t>https://artportalen.se/Sighting/97621009</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97621009</v>
+        <v>97620984</v>
       </c>
       <c r="B5" t="n">
-        <v>97733</v>
+        <v>96348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499664</v>
+        <v>499779</v>
       </c>
       <c r="R5" t="n">
-        <v>6592875</v>
+        <v>6592836</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,54 +1095,55 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97621009</t>
+          <t>https://artportalen.se/Sighting/97620984</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97620984</v>
+        <v>97611270</v>
       </c>
       <c r="B6" t="n">
-        <v>96348</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dammsjön SV, Vstm</t>
+          <t>Nora, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499779</v>
+        <v>499739</v>
       </c>
       <c r="R6" t="n">
-        <v>6592836</v>
+        <v>6592649</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,49 +1187,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97620984</t>
+          <t>https://artportalen.se/Sighting/97611270</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97611270</v>
+        <v>97610699</v>
       </c>
       <c r="B7" t="n">
-        <v>93197</v>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1244,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499739</v>
+        <v>499708</v>
       </c>
       <c r="R7" t="n">
-        <v>6592649</v>
+        <v>6592826</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1305,13 +1301,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97611270</t>
+          <t>https://artportalen.se/Sighting/97610699</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97610699</v>
+        <v>97610716</v>
       </c>
       <c r="B8" t="n">
         <v>91872</v>
@@ -1347,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499708</v>
+        <v>499709</v>
       </c>
       <c r="R8" t="n">
-        <v>6592826</v>
+        <v>6592814</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1408,13 +1404,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97610699</t>
+          <t>https://artportalen.se/Sighting/97610716</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97610716</v>
+        <v>97610787</v>
       </c>
       <c r="B9" t="n">
         <v>91872</v>
@@ -1450,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499709</v>
+        <v>499735</v>
       </c>
       <c r="R9" t="n">
-        <v>6592814</v>
+        <v>6592817</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1511,13 +1507,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97610716</t>
+          <t>https://artportalen.se/Sighting/97610787</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97610787</v>
+        <v>97610889</v>
       </c>
       <c r="B10" t="n">
         <v>91872</v>
@@ -1553,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499735</v>
+        <v>499721</v>
       </c>
       <c r="R10" t="n">
-        <v>6592817</v>
+        <v>6592788</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1586,9 +1582,19 @@
           <t>2021-12-18</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,24 +1609,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Ylva Wallin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Ylva Wallin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97610787</t>
+          <t>https://artportalen.se/Sighting/97610889</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97610889</v>
+        <v>97611775</v>
       </c>
       <c r="B11" t="n">
         <v>91872</v>
@@ -1656,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499721</v>
+        <v>499783</v>
       </c>
       <c r="R11" t="n">
-        <v>6592788</v>
+        <v>6592563</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1689,19 +1695,9 @@
           <t>2021-12-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1716,24 +1712,24 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ylva Wallin</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ylva Wallin</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97610889</t>
+          <t>https://artportalen.se/Sighting/97611775</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97611775</v>
+        <v>97611783</v>
       </c>
       <c r="B12" t="n">
         <v>91872</v>
@@ -1761,7 +1757,11 @@
           <t>(Schwein.) Murrill</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499783</v>
+        <v>499771</v>
       </c>
       <c r="R12" t="n">
-        <v>6592563</v>
+        <v>6592569</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1819,24 +1819,24 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Git Katarina Lundström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Git Katarina Lundström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97611775</t>
+          <t>https://artportalen.se/Sighting/97611783</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97611783</v>
+        <v>97620987</v>
       </c>
       <c r="B13" t="n">
         <v>91872</v>
@@ -1864,25 +1864,20 @@
           <t>(Schwein.) Murrill</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nora, Vstm</t>
+          <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499771</v>
+        <v>499783</v>
       </c>
       <c r="R13" t="n">
-        <v>6592569</v>
+        <v>6592763</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1926,27 +1921,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Git Katarina Lundström</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Git Katarina Lundström</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97611783</t>
+          <t>https://artportalen.se/Sighting/97620987</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97620987</v>
+        <v>137428937</v>
       </c>
       <c r="B14" t="n">
-        <v>91872</v>
+        <v>92148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,16 +1967,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>499783</v>
+        <v>499784</v>
       </c>
       <c r="R14" t="n">
-        <v>6592763</v>
+        <v>6592769</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2008,12 +2006,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2022,33 +2020,34 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97620987</t>
+          <t>https://artportalen.se/Sighting/137428937</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137428937</v>
+        <v>97621006</v>
       </c>
       <c r="B15" t="n">
-        <v>92148</v>
+        <v>80467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,34 +2055,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>499784</v>
+        <v>499734</v>
       </c>
       <c r="R15" t="n">
         <v>6592769</v>
@@ -2113,12 +2109,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2021-12-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2021-12-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2127,76 +2123,76 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137428937</t>
+          <t>https://artportalen.se/Sighting/97621006</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137427830</v>
+        <v>137424153</v>
       </c>
       <c r="B16" t="n">
-        <v>79535</v>
+        <v>58032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörtabäcken, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499729</v>
+        <v>499861</v>
       </c>
       <c r="R16" t="n">
-        <v>6592821</v>
+        <v>6592903</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2225,7 +2221,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2235,7 +2231,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,27 +2246,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anneli Sjöstrand</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anneli Sjöstrand</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137427830</t>
+          <t>https://artportalen.se/Sighting/137424153</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97621006</v>
+        <v>137425987</v>
       </c>
       <c r="B17" t="n">
-        <v>80467</v>
+        <v>58032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2278,37 +2274,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dammsjön SV, Vstm</t>
+          <t>Mörtabäcken, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499734</v>
+        <v>499984</v>
       </c>
       <c r="R17" t="n">
-        <v>6592769</v>
+        <v>6592946</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2332,12 +2333,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2352,24 +2363,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97621006</t>
+          <t>https://artportalen.se/Sighting/137425987</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137424153</v>
+        <v>137428916</v>
       </c>
       <c r="B18" t="n">
         <v>58032</v>
@@ -2397,25 +2408,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mörtabäcken, Vstm</t>
+          <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499861</v>
+        <v>499714</v>
       </c>
       <c r="R18" t="n">
-        <v>6592903</v>
+        <v>6592864</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2442,19 +2452,9 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2469,24 +2469,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137424153</t>
+          <t>https://artportalen.se/Sighting/137428916</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137425987</v>
+        <v>137428932</v>
       </c>
       <c r="B19" t="n">
         <v>58032</v>
@@ -2514,25 +2514,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mörtabäcken, Nora sn, Vstm</t>
+          <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499984</v>
+        <v>499982</v>
       </c>
       <c r="R19" t="n">
-        <v>6592946</v>
+        <v>6592826</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2559,19 +2558,9 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,44 +2575,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137425987</t>
+          <t>https://artportalen.se/Sighting/137428932</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137428916</v>
+        <v>97610586</v>
       </c>
       <c r="B20" t="n">
-        <v>58032</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2634,21 +2623,24 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dammsjön SV, Vstm</t>
+          <t>Nora, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>499714</v>
+        <v>499717</v>
       </c>
       <c r="R20" t="n">
-        <v>6592864</v>
+        <v>6592848</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2672,12 +2664,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2021-12-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2021-12-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2692,44 +2684,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137428916</t>
+          <t>https://artportalen.se/Sighting/97610586</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137428932</v>
+        <v>97611357</v>
       </c>
       <c r="B21" t="n">
-        <v>58032</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2740,21 +2732,24 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dammsjön SV, Vstm</t>
+          <t>Nora, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>499982</v>
+        <v>499757</v>
       </c>
       <c r="R21" t="n">
-        <v>6592826</v>
+        <v>6592561</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2778,12 +2773,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2021-12-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2021-12-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2798,24 +2793,24 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137428932</t>
+          <t>https://artportalen.se/Sighting/97611357</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>97610586</v>
+        <v>97612130</v>
       </c>
       <c r="B22" t="n">
         <v>57953</v>
@@ -2845,10 +2840,14 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2857,10 +2856,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>499717</v>
+        <v>499775</v>
       </c>
       <c r="R22" t="n">
-        <v>6592848</v>
+        <v>6592759</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2918,13 +2917,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97610586</t>
+          <t>https://artportalen.se/Sighting/97612130</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>97611357</v>
+        <v>97620996</v>
       </c>
       <c r="B23" t="n">
         <v>57953</v>
@@ -2953,26 +2952,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nora, Vstm</t>
+          <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>499757</v>
+        <v>499877</v>
       </c>
       <c r="R23" t="n">
-        <v>6592561</v>
+        <v>6592559</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3002,6 +2994,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hackspår på gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3016,76 +3013,70 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97611357</t>
+          <t>https://artportalen.se/Sighting/97620996</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>97612130</v>
+        <v>97620989</v>
       </c>
       <c r="B24" t="n">
-        <v>57953</v>
+        <v>4775</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nora, Vstm</t>
+          <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>499775</v>
+        <v>499789</v>
       </c>
       <c r="R24" t="n">
-        <v>6592759</v>
+        <v>6592695</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3129,62 +3120,67 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97612130</t>
+          <t>https://artportalen.se/Sighting/97620989</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>97620996</v>
+        <v>97620992</v>
       </c>
       <c r="B25" t="n">
-        <v>57953</v>
+        <v>4775</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>499877</v>
+        <v>499834</v>
       </c>
       <c r="R25" t="n">
-        <v>6592559</v>
+        <v>6592637</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3219,11 +3215,6 @@
           <t>2021-12-18</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hackspår på gran.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3247,13 +3238,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97620996</t>
+          <t>https://artportalen.se/Sighting/97620992</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>97620989</v>
+        <v>97620994</v>
       </c>
       <c r="B26" t="n">
         <v>4775</v>
@@ -3293,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>499789</v>
+        <v>499912</v>
       </c>
       <c r="R26" t="n">
-        <v>6592695</v>
+        <v>6592539</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3354,13 +3345,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97620989</t>
+          <t>https://artportalen.se/Sighting/97620994</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>97620992</v>
+        <v>97621003</v>
       </c>
       <c r="B27" t="n">
         <v>4775</v>
@@ -3400,10 +3391,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>499834</v>
+        <v>499714</v>
       </c>
       <c r="R27" t="n">
-        <v>6592637</v>
+        <v>6592733</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3461,13 +3452,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97620992</t>
+          <t>https://artportalen.se/Sighting/97621003</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>97620994</v>
+        <v>97621007</v>
       </c>
       <c r="B28" t="n">
         <v>4775</v>
@@ -3507,10 +3498,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>499912</v>
+        <v>499730</v>
       </c>
       <c r="R28" t="n">
-        <v>6592539</v>
+        <v>6592780</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3568,16 +3559,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97620994</t>
+          <t>https://artportalen.se/Sighting/97621007</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>97621003</v>
+        <v>97621002</v>
       </c>
       <c r="B29" t="n">
-        <v>4775</v>
+        <v>5179</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,39 +3576,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>499714</v>
+        <v>499717</v>
       </c>
       <c r="R29" t="n">
-        <v>6592733</v>
+        <v>6592666</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3675,16 +3661,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97621003</t>
+          <t>https://artportalen.se/Sighting/97621002</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>97621007</v>
+        <v>97621008</v>
       </c>
       <c r="B30" t="n">
-        <v>4775</v>
+        <v>5179</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3692,21 +3678,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3721,10 +3707,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>499730</v>
+        <v>499714</v>
       </c>
       <c r="R30" t="n">
-        <v>6592780</v>
+        <v>6592786</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3782,16 +3768,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97621007</t>
+          <t>https://artportalen.se/Sighting/97621008</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>97621002</v>
+        <v>97620995</v>
       </c>
       <c r="B31" t="n">
-        <v>5179</v>
+        <v>58327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3799,34 +3785,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>499717</v>
+        <v>499898</v>
       </c>
       <c r="R31" t="n">
-        <v>6592666</v>
+        <v>6592546</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3884,16 +3875,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97621002</t>
+          <t>https://artportalen.se/Sighting/97620995</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>97621008</v>
+        <v>137428918</v>
       </c>
       <c r="B32" t="n">
-        <v>5179</v>
+        <v>58191</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,42 +3892,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>103023</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Dammsjön SV, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>499714</v>
+        <v>499782</v>
       </c>
       <c r="R32" t="n">
-        <v>6592786</v>
+        <v>6592897</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3960,12 +3950,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3980,229 +3970,16 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/97621008</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>97620995</v>
-      </c>
-      <c r="B33" t="n">
-        <v>58327</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Regulus regulus</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Dammsjön SV, Vstm</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>499898</v>
-      </c>
-      <c r="R33" t="n">
-        <v>6592546</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/97620995</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>137428918</v>
-      </c>
-      <c r="B34" t="n">
-        <v>58191</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>103023</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Tofsmes</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Dammsjön SV, Vstm</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>499782</v>
-      </c>
-      <c r="R34" t="n">
-        <v>6592897</v>
-      </c>
-      <c r="S34" t="n">
-        <v>50</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Mattias Drejby</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Mattias Drejby</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137428918</t>
         </is>
@@ -4241,8 +4018,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42266-2026 artfynd.xlsx
+++ b/artfynd/A 42266-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137428938</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>137428937</v>
       </c>
       <c r="B14" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>137424153</v>
       </c>
       <c r="B16" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>137425987</v>
       </c>
       <c r="B17" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>137428916</v>
       </c>
       <c r="B18" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137428932</v>
       </c>
       <c r="B19" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>137428918</v>
       </c>
       <c r="B32" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
